--- a/Data/EXCEL/Transfer/salemon/202208/8433-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8433-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47696F8D-E574-4389-A19D-FAAF0750D996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3A12B83-BF77-422A-85DF-BA23ABF79943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8433-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,22 +1227,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q138"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="9" width="10.125" customWidth="1"/>
-    <col min="10" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="11" width="10.125" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="14" width="10.125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1261,7 +1269,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1300,7 +1308,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1343,7 +1351,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1382,7 +1390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1435,7 +1443,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1488,7 +1496,7 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1541,7 +1549,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1594,7 +1602,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1647,7 +1655,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1700,7 +1708,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1753,7 +1761,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1806,7 +1814,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1859,7 +1867,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1912,7 +1920,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1965,7 +1973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2018,7 +2026,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2071,7 +2079,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2124,7 +2132,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2177,7 +2185,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2230,7 +2238,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2283,7 +2291,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2336,7 +2344,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2389,7 +2397,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2442,7 +2450,7 @@
         <v>-7.15</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2495,7 +2503,7 @@
         <v>-21.4</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2548,7 +2556,7 @@
         <v>-22.4</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2601,7 +2609,7 @@
         <v>-24.4</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2654,7 +2662,7 @@
         <v>-27.2</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2707,7 +2715,7 @@
         <v>-29.6</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2760,7 +2768,7 @@
         <v>-29.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2813,7 +2821,7 @@
         <v>-29.5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2866,7 +2874,7 @@
         <v>-27.5</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2919,7 +2927,7 @@
         <v>-21.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2972,7 +2980,7 @@
         <v>-16.5</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3025,7 +3033,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3078,7 +3086,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3131,7 +3139,7 @@
         <v>-7.54</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3184,7 +3192,7 @@
         <v>-7.07</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3237,7 +3245,7 @@
         <v>-8.26</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3290,7 +3298,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3343,7 +3351,7 @@
         <v>-9.41</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3396,7 +3404,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3449,7 +3457,7 @@
         <v>-11.6</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3502,7 +3510,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3555,7 +3563,7 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3608,7 +3616,7 @@
         <v>-19.2</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3661,7 +3669,7 @@
         <v>-21</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3714,7 +3722,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3767,7 +3775,7 @@
         <v>9.3699999999999992</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3820,7 +3828,7 @@
         <v>8.06</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3873,7 +3881,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3926,7 +3934,7 @@
         <v>7.05</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3979,7 +3987,7 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4032,7 +4040,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4085,7 +4093,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4138,7 +4146,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4191,7 +4199,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4244,7 +4252,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4297,7 +4305,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4350,7 +4358,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4403,7 +4411,7 @@
         <v>-1.54</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4456,7 +4464,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4509,7 +4517,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4562,7 +4570,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4615,7 +4623,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4668,7 +4676,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4721,7 +4729,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4774,7 +4782,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4827,7 +4835,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4880,7 +4888,7 @@
         <v>-3.75</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4933,7 +4941,7 @@
         <v>-6.1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4986,7 +4994,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5039,7 +5047,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5092,7 +5100,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5145,7 +5153,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5198,7 +5206,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5251,7 +5259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5304,7 +5312,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5357,7 +5365,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5410,7 +5418,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5463,7 +5471,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5516,7 +5524,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5569,7 +5577,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5622,7 +5630,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5675,7 +5683,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5728,7 +5736,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5781,7 +5789,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5834,7 +5842,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5887,7 +5895,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5940,7 +5948,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5993,7 +6001,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6046,7 +6054,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6099,7 +6107,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6152,7 +6160,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6205,7 +6213,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6258,7 +6266,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6311,7 +6319,7 @@
         <v>-13.6</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6364,7 +6372,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6417,7 +6425,7 @@
         <v>-16.5</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6470,7 +6478,7 @@
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6523,7 +6531,7 @@
         <v>-17.5</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6576,7 +6584,7 @@
         <v>-16.5</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6629,7 +6637,7 @@
         <v>-20.3</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6682,7 +6690,7 @@
         <v>-15.4</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6735,7 +6743,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6788,7 +6796,7 @@
         <v>-7.54</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6841,7 +6849,7 @@
         <v>-0.74</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6894,7 +6902,7 @@
         <v>-31.3</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6947,7 +6955,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -7000,7 +7008,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7053,7 +7061,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7106,7 +7114,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7159,7 +7167,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7212,7 +7220,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7265,7 +7273,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7318,7 +7326,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7371,7 +7379,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7424,7 +7432,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7477,7 +7485,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7530,7 +7538,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7583,7 +7591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7636,7 +7644,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7689,7 +7697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7742,7 +7750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7795,7 +7803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7848,7 +7856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7901,7 +7909,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7954,7 +7962,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8007,7 +8015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8060,7 +8068,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8113,7 +8121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8166,7 +8174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8219,7 +8227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8272,7 +8280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8325,7 +8333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8378,7 +8386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8431,7 +8439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8499,7 +8507,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>